--- a/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/NCDDutyOfCare.xlsx
+++ b/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/NCDDutyOfCare.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://defra-my.sharepoint.com/personal/william_skalka_defra_gov_uk/Documents/Documents/GitHub/ea-wigan-waste-transfer-notes/Wigan Transfer Note Data Extraction/Assets/Spreadsheet Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{8D328007-643D-4387-B249-36E45171352B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3751C439-D39F-4698-819F-55F476CC896F}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{8D328007-643D-4387-B249-36E45171352B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2763845A-9E46-4699-9A25-6086313D433B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3D87BFF-B695-4E3E-B3C1-CE00A55FE5AF}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>Registration Number (Section C)</t>
   </si>
   <si>
-    <t>Vehicle Registration (Section C)</t>
-  </si>
-  <si>
     <t>D1 Address of Transfer</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Details (Section C)</t>
   </si>
 </sst>
 </file>
@@ -160,10 +160,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -492,7 +488,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -534,31 +530,31 @@
         <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
